--- a/assets/fonte/criticas_pos_processamento_5050.xlsx
+++ b/assets/fonte/criticas_pos_processamento_5050.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\Fonte DRO - 5050\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\conversor_dro_5050 3\assets\fonte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6941DC09-AA70-4FFF-AF66-ECE584B580CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D94AE1-EB34-4D92-8FFF-ACE433092119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9120" yWindow="345" windowWidth="31005" windowHeight="17355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3630" yWindow="3225" windowWidth="24675" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Criticas Pos" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="108">
   <si>
     <t>Código</t>
   </si>
@@ -343,6 +343,12 @@
   </si>
   <si>
     <t>Principiologicamente, não é esperado que haja provisão para eventos de fraude.</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Coluna1</t>
   </si>
 </sst>
 </file>
@@ -554,13 +560,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="CriticasPosProcessamento" displayName="CriticasPosProcessamento" ref="A1:E27">
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="CriticasPosProcessamento" displayName="CriticasPosProcessamento" ref="A1:F27">
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Código"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Descrição"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Campos avaliados"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Observações"/>
+    <tableColumn id="6" xr3:uid="{75C57824-B385-4BA8-971B-A2D345E64DD9}" name="Coluna1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -715,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -725,7 +732,7 @@
     <col min="5" max="5" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27.95" customHeight="1">
+    <row r="1" spans="1:6" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -741,8 +748,11 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="66" customHeight="1">
+      <c r="F1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="66" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -758,8 +768,11 @@
       <c r="E2" s="16" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="66" customHeight="1">
+      <c r="F2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="66" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>10</v>
       </c>
@@ -775,8 +788,11 @@
       <c r="E3" s="17" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="66" customHeight="1">
+      <c r="F3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="66" customHeight="1">
       <c r="A4" s="8" t="s">
         <v>13</v>
       </c>
@@ -792,8 +808,11 @@
       <c r="E4" s="18" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="66" customHeight="1">
+      <c r="F4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="66" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>17</v>
       </c>
@@ -809,8 +828,11 @@
       <c r="E5" s="17" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="66" customHeight="1">
+      <c r="F5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="66" customHeight="1">
       <c r="A6" s="8" t="s">
         <v>21</v>
       </c>
@@ -826,8 +848,11 @@
       <c r="E6" s="18" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="66" customHeight="1">
+      <c r="F6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="66" customHeight="1">
       <c r="A7" s="6" t="s">
         <v>25</v>
       </c>
@@ -843,8 +868,11 @@
       <c r="E7" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="66" customHeight="1">
+      <c r="F7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="66" customHeight="1">
       <c r="A8" s="8" t="s">
         <v>29</v>
       </c>
@@ -860,8 +888,11 @@
       <c r="E8" s="18" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="66" customHeight="1">
+      <c r="F8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="66" customHeight="1">
       <c r="A9" s="6" t="s">
         <v>33</v>
       </c>
@@ -877,8 +908,11 @@
       <c r="E9" s="17" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="66" customHeight="1">
+      <c r="F9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="66" customHeight="1">
       <c r="A10" s="8" t="s">
         <v>37</v>
       </c>
@@ -894,8 +928,11 @@
       <c r="E10" s="18" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="66" customHeight="1">
+      <c r="F10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="66" customHeight="1">
       <c r="A11" s="6" t="s">
         <v>41</v>
       </c>
@@ -911,8 +948,11 @@
       <c r="E11" s="17" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="66" customHeight="1">
+      <c r="F11" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="66" customHeight="1">
       <c r="A12" s="8" t="s">
         <v>45</v>
       </c>
@@ -928,8 +968,11 @@
       <c r="E12" s="18" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="66" customHeight="1">
+      <c r="F12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="66" customHeight="1">
       <c r="A13" s="6" t="s">
         <v>49</v>
       </c>
@@ -945,8 +988,11 @@
       <c r="E13" s="17" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="66" customHeight="1">
+      <c r="F13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="66" customHeight="1">
       <c r="A14" s="8" t="s">
         <v>53</v>
       </c>
@@ -963,7 +1009,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="66" customHeight="1">
+    <row r="15" spans="1:6" ht="66" customHeight="1">
       <c r="A15" s="6" t="s">
         <v>57</v>
       </c>
@@ -980,7 +1026,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="66" customHeight="1">
+    <row r="16" spans="1:6" ht="66" customHeight="1">
       <c r="A16" s="8" t="s">
         <v>61</v>
       </c>
@@ -996,8 +1042,11 @@
       <c r="E16" s="18" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="66" customHeight="1">
+      <c r="F16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="66" customHeight="1">
       <c r="A17" s="6" t="s">
         <v>64</v>
       </c>
@@ -1013,8 +1062,11 @@
       <c r="E17" s="17" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="66" customHeight="1">
+      <c r="F17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="66" customHeight="1">
       <c r="A18" s="8" t="s">
         <v>67</v>
       </c>
@@ -1030,8 +1082,11 @@
       <c r="E18" s="18" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="66" customHeight="1">
+      <c r="F18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="66" customHeight="1">
       <c r="A19" s="6" t="s">
         <v>71</v>
       </c>
@@ -1048,7 +1103,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="66" customHeight="1">
+    <row r="20" spans="1:6" ht="66" customHeight="1">
       <c r="A20" s="8" t="s">
         <v>75</v>
       </c>
@@ -1064,8 +1119,11 @@
       <c r="E20" s="18" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="66" customHeight="1">
+      <c r="F20" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="66" customHeight="1">
       <c r="A21" s="6" t="s">
         <v>78</v>
       </c>
@@ -1081,8 +1139,11 @@
       <c r="E21" s="17" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="66" customHeight="1">
+      <c r="F21" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="66" customHeight="1">
       <c r="A22" s="8" t="s">
         <v>82</v>
       </c>
@@ -1099,7 +1160,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="66" customHeight="1">
+    <row r="23" spans="1:6" ht="66" customHeight="1">
       <c r="A23" s="6" t="s">
         <v>86</v>
       </c>
@@ -1116,7 +1177,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="66" customHeight="1">
+    <row r="24" spans="1:6" ht="66" customHeight="1">
       <c r="A24" s="8" t="s">
         <v>90</v>
       </c>
@@ -1133,7 +1194,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="66" customHeight="1">
+    <row r="25" spans="1:6" ht="66" customHeight="1">
       <c r="A25" s="6" t="s">
         <v>94</v>
       </c>
@@ -1150,7 +1211,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="66" customHeight="1">
+    <row r="26" spans="1:6" ht="66" customHeight="1">
       <c r="A26" s="8" t="s">
         <v>98</v>
       </c>
@@ -1167,7 +1228,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="66" customHeight="1">
+    <row r="27" spans="1:6" ht="66" customHeight="1">
       <c r="A27" s="10" t="s">
         <v>102</v>
       </c>
@@ -1182,6 +1243,9 @@
       </c>
       <c r="E27" s="19" t="s">
         <v>105</v>
+      </c>
+      <c r="F27" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
